--- a/results/greedy/UAVs8_GRID13/tour/UAVs8_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs8_GRID13/tour/UAVs8_GRID13_1920_16_Greedy_sequences.xlsx
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0224674170021899</v>
+        <v>0.02370829100254923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932045899797231</v>
+        <v>0.02835066599072888</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02399454201804474</v>
+        <v>0.02259466703981161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02508416696218774</v>
+        <v>0.02461170899914578</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02881166600855067</v>
+        <v>0.02879850001772866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02735091699287295</v>
+        <v>0.02706970798317343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02226350002456456</v>
+        <v>0.02172637503826991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02603062498383224</v>
+        <v>0.0252170410240069</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01959683297900483</v>
+        <v>0.01936249999562278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01940970902796835</v>
+        <v>0.01992349995998666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02485350001370534</v>
+        <v>0.02432645799126476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02428095805225894</v>
+        <v>0.02401358296629041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02372533298330382</v>
+        <v>0.02432170801330358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02633508399594575</v>
+        <v>0.02662600000621751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02523654204560444</v>
+        <v>0.02495704096509144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02228545799152926</v>
+        <v>0.02174804196693003</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02170541702071205</v>
+        <v>0.02205133304232731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0251744159613736</v>
+        <v>0.02727050002431497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02648741699522361</v>
+        <v>0.02724795899121091</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02023541700327769</v>
+        <v>0.0200036249589175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02211845899000764</v>
+        <v>0.02190833300119266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02721629198640585</v>
+        <v>0.02761345799081028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02832116698846221</v>
+        <v>0.0277420420316048</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02648670802591369</v>
+        <v>0.0274296670104377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02579241700004786</v>
+        <v>0.02577400003792718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02307175000896677</v>
+        <v>0.02331679104827344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02066112495958805</v>
+        <v>0.02033645904157311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.024465250025969</v>
+        <v>0.02563774998998269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01895375002641231</v>
+        <v>0.01967616699403152</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02497816696995869</v>
+        <v>0.02468549995683134</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02330600004643202</v>
+        <v>0.02369133400497958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02264354203362018</v>
+        <v>0.02254258305765688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02041429199744016</v>
+        <v>0.02070191700477153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0261858330341056</v>
+        <v>0.02575050003360957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02636937500210479</v>
+        <v>0.02718437497969717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02532616700045764</v>
+        <v>0.03463154099881649</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02446150005562231</v>
+        <v>0.02407362504163757</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0216537500382401</v>
+        <v>0.02163479197770357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02764395897975191</v>
+        <v>0.02734054200118408</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01936595799634233</v>
+        <v>0.02217904198914766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01750704098958522</v>
+        <v>0.0206299580167979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01847462495788932</v>
+        <v>0.0191565829445608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02065691701136529</v>
+        <v>0.02246516599552706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02318300004117191</v>
+        <v>0.02296741597820073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02359987498493865</v>
+        <v>0.02521383401472121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02276970900129527</v>
+        <v>0.02256820804905146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02119391702581197</v>
+        <v>0.02895220898790285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02216804202180356</v>
+        <v>0.04011829098453745</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02522695902734995</v>
+        <v>0.02510104200337082</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02465445903362706</v>
+        <v>0.02547925000544637</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02023920899955556</v>
+        <v>0.02240945800440386</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01887283398536965</v>
+        <v>0.0194754580152221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02325954200932756</v>
+        <v>0.04090437496779487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02110166702186689</v>
+        <v>0.02087820798624307</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02102520799962804</v>
+        <v>0.02053891698596999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387570805149153</v>
+        <v>0.02761195896891877</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02693520800676197</v>
+        <v>0.02687770797638223</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01766858296468854</v>
+        <v>0.01731541700428352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02388454199535772</v>
+        <v>0.02333533402998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02030587499029934</v>
+        <v>0.01983424997888505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02035604103002697</v>
+        <v>0.01987320894841105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0292802500189282</v>
+        <v>0.02918987500015646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.028609958011657</v>
+        <v>0.02838204201543704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02702570799738169</v>
+        <v>0.02627899998333305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01897387497592717</v>
+        <v>0.01921549998223782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01991062500746921</v>
+        <v>0.02030995895620435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02427962503861636</v>
+        <v>0.02396558300824836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02480479096993804</v>
+        <v>0.0244318749755621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02366595802595839</v>
+        <v>0.02335095900343731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02716733299894258</v>
+        <v>0.02923945803195238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02776795800309628</v>
+        <v>0.02774858300108463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02072700002463534</v>
+        <v>0.02045020798686892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02288537501590326</v>
+        <v>0.0226302079972811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02316758298547938</v>
+        <v>0.02392141701420769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01715545903425664</v>
+        <v>0.01819495903328061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02172899997094646</v>
+        <v>0.02209041605237871</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02860470896121114</v>
+        <v>0.02850312500959262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02372999995714054</v>
+        <v>0.024384958029259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01532075001159683</v>
+        <v>0.01525699999183416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02610158396419138</v>
+        <v>0.0268787500099279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02580170897999778</v>
+        <v>0.03355724998982623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02156987501075491</v>
+        <v>0.02288154099369422</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02409179101232439</v>
+        <v>0.02349475002847612</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02035220799734816</v>
+        <v>0.02092375000938773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02630337496520951</v>
+        <v>0.02605079195927829</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02358195901615545</v>
+        <v>0.02332666702568531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02689824998378754</v>
+        <v>0.02710683300392702</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02774120902176946</v>
+        <v>0.02946791599970311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03380862501217052</v>
+        <v>0.03306908399099484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02392762503586709</v>
+        <v>0.03986387501936406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0195541669963859</v>
+        <v>0.01925995800411329</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02705720899393782</v>
+        <v>0.02634758298518136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02206720795948058</v>
+        <v>0.02168904099380597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02497637498890981</v>
+        <v>0.0243458750192076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02445791702484712</v>
+        <v>0.02410483302082866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02311499998904765</v>
+        <v>0.02405462501337752</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02443395805312321</v>
+        <v>0.0241453749476932</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03014595899730921</v>
+        <v>0.02979562495602295</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387087501119822</v>
+        <v>0.02330266701756045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0241272080456838</v>
+        <v>0.02369066601386294</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/results/greedy/UAVs8_GRID13/tour/UAVs8_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs8_GRID13/tour/UAVs8_GRID13_1920_16_Greedy_sequences.xlsx
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02370829100254923</v>
+        <v>0.02242045802995563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02835066599072888</v>
+        <v>0.02881420898484066</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02259466703981161</v>
+        <v>0.02234908397076651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02461170899914578</v>
+        <v>0.02493800001684576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02879850001772866</v>
+        <v>0.02818741695955396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02706970798317343</v>
+        <v>0.02668099995935336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02172637503826991</v>
+        <v>0.02149233297677711</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0252170410240069</v>
+        <v>0.02676587499445304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01936249999562278</v>
+        <v>0.01883770799031481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01992349995998666</v>
+        <v>0.01878604100784287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02432645799126476</v>
+        <v>0.02466979197924957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02401358296629041</v>
+        <v>0.02376529097091407</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02432170801330358</v>
+        <v>0.02304254099726677</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02662600000621751</v>
+        <v>0.02583224995760247</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02495704096509144</v>
+        <v>0.02490729198325425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02174804196693003</v>
+        <v>0.02153091697255149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02205133304232731</v>
+        <v>0.02117429202189669</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02727050002431497</v>
+        <v>0.02477587503381073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02724795899121091</v>
+        <v>0.02630833303555846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0200036249589175</v>
+        <v>0.01964924996718764</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02190833300119266</v>
+        <v>0.0213653749669902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761345799081028</v>
+        <v>0.02726029098266736</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0277420420316048</v>
+        <v>0.02745149994734675</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0274296670104377</v>
+        <v>0.0259606660110876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02577400003792718</v>
+        <v>0.02521441702265292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02331679104827344</v>
+        <v>0.02253204100998119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02033645904157311</v>
+        <v>0.02022641699295491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02563774998998269</v>
+        <v>0.02354708302300423</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01967616699403152</v>
+        <v>0.01841354096541181</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02468549995683134</v>
+        <v>0.02471612504450604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02369133400497958</v>
+        <v>0.02289383299648762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02254258305765688</v>
+        <v>0.0221787909977138</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02070191700477153</v>
+        <v>0.02093120798235759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02575050003360957</v>
+        <v>0.02583054103888571</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02718437497969717</v>
+        <v>0.02627283299807459</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03463154099881649</v>
+        <v>0.02529687498463318</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02407362504163757</v>
+        <v>0.0239944169879891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02163479197770357</v>
+        <v>0.02210066700354218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02734054200118408</v>
+        <v>0.02791695803171024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02217904198914766</v>
+        <v>0.01980170799652115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0206299580167979</v>
+        <v>0.01708174997474998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0191565829445608</v>
+        <v>0.01805300003616139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02246516599552706</v>
+        <v>0.02081641700351611</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02296741597820073</v>
+        <v>0.02280541695654392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02521383401472121</v>
+        <v>0.02380745799746364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02256820804905146</v>
+        <v>0.02272695902502164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02895220898790285</v>
+        <v>0.02159404201665893</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04011829098453745</v>
+        <v>0.02161674998933449</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02510104200337082</v>
+        <v>0.02509650000138208</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02547925000544637</v>
+        <v>0.02502433402696624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02240945800440386</v>
+        <v>0.02082295902073383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0194754580152221</v>
+        <v>0.01980670902412385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04090437496779487</v>
+        <v>0.02296941704116762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02087820798624307</v>
+        <v>0.0206593339680694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02053891698596999</v>
+        <v>0.02080508298240602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761195896891877</v>
+        <v>0.02363166701979935</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02687770797638223</v>
+        <v>0.02787425002316013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01731541700428352</v>
+        <v>0.01821154198842123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02333533402998</v>
+        <v>0.02361316699534655</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01983424997888505</v>
+        <v>0.02059004199691117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01987320894841105</v>
+        <v>0.0201097919489257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02918987500015646</v>
+        <v>0.02879987499909475</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02838204201543704</v>
+        <v>0.02798116696067154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627899998333305</v>
+        <v>0.02661266596987844</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01921549998223782</v>
+        <v>0.01900224998826161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02030995895620435</v>
+        <v>0.0203281250433065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02396558300824836</v>
+        <v>0.02502133295638487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0244318749755621</v>
+        <v>0.02481258398620412</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02335095900343731</v>
+        <v>0.02473879099125043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02923945803195238</v>
+        <v>0.02742087497608736</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02774858300108463</v>
+        <v>0.02725941699463874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02045020798686892</v>
+        <v>0.02108570898417383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0226302079972811</v>
+        <v>0.02296699996804819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02392141701420769</v>
+        <v>0.02346570894587785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01819495903328061</v>
+        <v>0.01776191702811047</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02209041605237871</v>
+        <v>0.02229074999922886</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02850312500959262</v>
+        <v>0.02827454201178625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.024384958029259</v>
+        <v>0.02338774997042492</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01525699999183416</v>
+        <v>0.01517133397283033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0268787500099279</v>
+        <v>0.02615120896371081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03355724998982623</v>
+        <v>0.02528179198270664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02288154099369422</v>
+        <v>0.02112275001127273</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02349475002847612</v>
+        <v>0.02310383302392438</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02092375000938773</v>
+        <v>0.01989554200554267</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02605079195927829</v>
+        <v>0.02588841697433963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02332666702568531</v>
+        <v>0.02351649996126071</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02710683300392702</v>
+        <v>0.02723733300808817</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02946791599970311</v>
+        <v>0.02726404200075194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03306908399099484</v>
+        <v>0.03300837497226894</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03986387501936406</v>
+        <v>0.02326550002908334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01925995800411329</v>
+        <v>0.01960041699931026</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02634758298518136</v>
+        <v>0.02655220800079405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02168904099380597</v>
+        <v>0.02178037504199892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0243458750192076</v>
+        <v>0.02409625001018867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02410483302082866</v>
+        <v>0.02387025003554299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02405462501337752</v>
+        <v>0.02249995898455381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0241453749476932</v>
+        <v>0.02353916695574299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02979562495602295</v>
+        <v>0.02944445802131668</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02330266701756045</v>
+        <v>0.02322824997827411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02369066601386294</v>
+        <v>0.02377024997258559</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
